--- a/result/cluster_analysis_all_proteins_outlier_group2.xlsx
+++ b/result/cluster_analysis_all_proteins_outlier_group2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F1"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,582 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>365</v>
+      </c>
+      <c r="B2" t="n">
+        <v>12.83471775054932</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.597990751266479</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AF-P0CE87-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>51.29713414634147</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>YPL282C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="B3" t="n">
+        <v>12.80373001098633</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.566285014152527</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AF-P53427-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>68.459</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>YLR461W</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>527</v>
+      </c>
+      <c r="B4" t="n">
+        <v>12.8035249710083</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.569655418395996</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AF-P0CE88-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>69.56858333333334</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>YJL223C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>654</v>
+      </c>
+      <c r="B5" t="n">
+        <v>12.80376148223877</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.564398527145386</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AF-P0CE91-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>69.23308333333333</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>YLL064C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>779</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12.80458164215088</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.564999580383301</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AF-P35994-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>69.04764227642276</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>YKL224C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>1638</v>
+      </c>
+      <c r="B7" t="n">
+        <v>12.75671577453613</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.594103693962097</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AF-Q8TGT6-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>73.43896551724139</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YHR022C-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>2181</v>
+      </c>
+      <c r="B8" t="n">
+        <v>12.78017044067383</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.546092510223389</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AF-Q07987-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>68.90274193548387</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>YLR037C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>2549</v>
+      </c>
+      <c r="B9" t="n">
+        <v>12.81541728973389</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.576052665710449</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AF-P0CE86-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>52.38914634146342</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>YOR394W</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>2670</v>
+      </c>
+      <c r="B10" t="n">
+        <v>12.80439758300781</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.565769791603088</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AF-P38155-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>69.98416666666665</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>YBR301W</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>2703</v>
+      </c>
+      <c r="B11" t="n">
+        <v>12.80398845672607</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.564592003822327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AF-P0CE89-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>69.6095</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>YIL176C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>2861</v>
+      </c>
+      <c r="B12" t="n">
+        <v>12.80325508117676</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.564324140548706</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AF-P53343-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>70.74541666666667</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>YGR294W</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>3056</v>
+      </c>
+      <c r="B13" t="n">
+        <v>12.80397319793701</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.567801475524902</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AF-P0CE90-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>69.52800000000001</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>YNR076W</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>3158</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12.80199813842773</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.567740678787231</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AF-Q03050-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>68.94608333333332</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>YDR542W</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>3233</v>
+      </c>
+      <c r="B15" t="n">
+        <v>12.80303478240967</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.564088940620422</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AF-P43575-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>71.13885245901638</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>YFL020C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>3467</v>
+      </c>
+      <c r="B16" t="n">
+        <v>12.7974796295166</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.562059760093689</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AF-P40585-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>68.90370967741937</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>YIR041W</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>3652</v>
+      </c>
+      <c r="B17" t="n">
+        <v>12.79530429840088</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.560587763786316</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AF-Q12370-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>68.67556451612906</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>YLL025W</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>3943</v>
+      </c>
+      <c r="B18" t="n">
+        <v>12.80586338043213</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.566599369049072</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AF-P32612-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>69.68541666666667</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>YEL049W</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>4258</v>
+      </c>
+      <c r="B19" t="n">
+        <v>12.8032865524292</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.567757725715637</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AF-Q08322-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>69.14941666666667</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>YOL161C</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>4277</v>
+      </c>
+      <c r="B20" t="n">
+        <v>12.81699180603027</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.555652141571045</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AF-Q3E770-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>69.31066666666668</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>YBL108C-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>4337</v>
+      </c>
+      <c r="B21" t="n">
+        <v>12.79560279846191</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.577208518981934</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AF-P0CE92-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>69.51008333333333</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>YAL068C</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>4721</v>
+      </c>
+      <c r="B22" t="n">
+        <v>12.79305171966553</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.558775901794434</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AF-P0CE85-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>74.09403225806452</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>YMR325W</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>4962</v>
+      </c>
+      <c r="B23" t="n">
+        <v>12.80620384216309</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.570106625556946</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AF-P0CE93-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>68.27874999999999</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>YGL261C</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>5766</v>
+      </c>
+      <c r="B24" t="n">
+        <v>12.80078983306885</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.563297033309937</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AF-P38725-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>68.50874999999999</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>YHL046C</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>5873</v>
+      </c>
+      <c r="B25" t="n">
+        <v>12.7839469909668</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.548937559127808</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AF-P25610-F1-model_v1.pdb</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>68.34354838709677</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>YCR104W</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
